--- a/artfynd/A 61818-2022 artfynd.xlsx
+++ b/artfynd/A 61818-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61818-2022 artfynd.xlsx
+++ b/artfynd/A 61818-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83669118</v>
+        <v>75073824</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,25 +705,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ältsjön, Upl</t>
+          <t>Ältsjön SV om Länna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664431.7049193794</v>
+        <v>664437</v>
       </c>
       <c r="R2" t="n">
-        <v>6640298.009620027</v>
+        <v>6640325</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,33 +747,23 @@
           <t>Almunge</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7CD98ED5-CB12-4485-9F23-27C8562530B4</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-02-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-11-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-02-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2003-11-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 dm2 på död, kvarsittande gren på levande ek, omkr. 324 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -784,34 +771,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Död, kvarsittande gren på levande ek. # Skogsek</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>99396069</v>
       </c>
       <c r="B3" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664428.4914868412</v>
+        <v>664428</v>
       </c>
       <c r="R3" t="n">
-        <v>6640325.02191499</v>
+        <v>6640325</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +867,9 @@
           <t>2022-03-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-03-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
